--- a/data/batches/B14_TrialSummary_TS_part2/Test_Validation_Report/Test_Validation_Report_B14.xlsx
+++ b/data/batches/B14_TrialSummary_TS_part2/Test_Validation_Report/Test_Validation_Report_B14.xlsx
@@ -2129,11 +2129,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2208,11 +2204,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2287,11 +2279,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2366,11 +2354,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2445,11 +2429,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2524,11 +2504,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2603,11 +2579,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2682,11 +2654,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2761,11 +2729,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2840,11 +2804,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2919,11 +2879,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2998,11 +2954,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -3077,11 +3029,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -3156,11 +3104,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -3235,11 +3179,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
